--- a/光伏配储项目/电价数据/2026/岭南厂.xlsx
+++ b/光伏配储项目/电价数据/2026/岭南厂.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.51057</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.39552</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7522300000000001</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.57378</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.59262</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.52375</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.50912</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43767</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.4545</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42424</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.4213</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.4089</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39897</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40286</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40292</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39158</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41704</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.3921</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42072</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.414</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42399</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41377</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44512</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.37738</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.35689</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.32906</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.30295</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.12344</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.10096</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.1132</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.10021</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.12416</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.09759000000000001</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.13419</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.19838</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.32052</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08929000000000001</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.07654000000000001</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.01749</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14813</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21471</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.24228</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.47134</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.22925</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.17542</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.01919</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.5949099999999999</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.14582</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.40719</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.27795</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.44653</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.40754</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.20169</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.30848</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.60561</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.53579</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.53728</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.33674</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.40353</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.6120099999999999</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.4489</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.44911</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.46281</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.5704900000000001</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.46663</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.61054</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.80113</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.6323799999999999</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.63849</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.7696900000000001</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.82586</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.42535</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.6792699999999999</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.59896</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.74139</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.6960599999999999</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.7460599999999999</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.6483099999999999</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.6147699999999999</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.5280900000000001</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48653</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.47474</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.43357</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.70253</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.84301</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.75241</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.9119700000000001</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5481699999999999</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.5194800000000001</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5064</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50906</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48863</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40283</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47069</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38125</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39205</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37124</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35665</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36286</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37602</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37602</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.41983</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.5039399999999999</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.61248</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.8186</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.42837</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.39722</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.4567</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.36795</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.4495</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.5137</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.36267</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.36103</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.36329</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.38495</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.34189</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.33234</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.33814</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.42286</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.47283</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.72737</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>1.01534</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.6784199999999999</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.83287</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.75727</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.68191</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.74695</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.51036</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.90262</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.84562</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.27814</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.43196</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.36849</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.48848</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.33847</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.49501</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.5302100000000001</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.99864</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.6765599999999999</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.60123</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.5942000000000001</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.59373</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.61136</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.4016</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.79689</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.57143</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.34801</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.6264500000000001</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.76947</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.57792</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.67265</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.80174</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.7155</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.65259</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.61878</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.76425</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.6159199999999999</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.44025</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.19275</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.37221</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.45207</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.7162500000000001</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.4401</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43352</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.41362</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33631</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.3214</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.5137</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.49041</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.45536</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.4194</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36547</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35639</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.37245</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.36337</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39644</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47387</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44431</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35387</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.37075</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.35172</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.37466</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.32463</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.31735</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.21389</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.38331</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.34164</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.34495</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.35878</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.3501</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.57165</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.5073</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.07975</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.35077</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.63593</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.65666</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.49805</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.5286799999999999</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.5786699999999999</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.64406</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.66579</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.32707</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.36989</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.42298</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.3919</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.40854</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.6486000000000001</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.41979</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.48137</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.5558200000000001</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.5739</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.91698</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.38262</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.38374</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.5454600000000001</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.61953</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.65266</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.5932500000000001</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.33079</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.4826</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.43618</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.50944</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.42035</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.4682</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.44585</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.46696</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.45295</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.40817</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.38275</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.432</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.41066</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.40224</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.40662</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36737</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.3432</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.52843</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.46533</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.37811</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.36645</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.36292</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.34257</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.36745</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45848</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.3438</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.32891</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.34212</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.34374</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.34342</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.3112</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.3176</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.31766</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.30657</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.30689</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.31173</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.36158</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34955</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.34906</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.31755</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.3439700000000001</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.34731</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.28737</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.26873</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.31745</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.10284</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.21975</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.19833</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.31579</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.28067</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.24028</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.301</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.50431</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.30452</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.40399</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.33707</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.33355</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.32761</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.12697</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.29424</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.49496</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.44092</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.50182</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.35919</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.5249299999999999</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.33242</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34241</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.45822</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.31251</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.23009</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.2821</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.29376</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.27438</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.1476</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.26286</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.28232</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.30376</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.33458</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.31591</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.4931</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.74897</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.5088199999999999</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.43793</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.3692</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.35427</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.3721</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.37082</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.32664</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.33717</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.32982</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.30967</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.32247</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.32974</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.3001</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.45677</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.37923</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35452</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.33047</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32111</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.32209</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.31956</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31579</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.3092</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.30974</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.30396</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.29926</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31404</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31427</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.32088</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.30457</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31167</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.31383</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31447</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31363</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.327</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.32317</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.32664</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.34573</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.3433</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.33822</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.3339</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.3339</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.28818</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.33453</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.1761</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.30284</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.21842</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.1982</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.15395</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.33235</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.33344</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.21904</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.3252</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.35184</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.04387</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.41444</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.10314</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.2901</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.293</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3393</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33537</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.38807</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.3923</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38596</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37661</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.3413</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46752</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39642</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.41614</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35808</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35523</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.351</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.368</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.6687000000000001</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44602</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35891</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33411</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.3001</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33531</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.1025</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.0483</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.76478</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.07074999999999999</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.32861</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.10772</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.30541</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.46675</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.00517</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.18337</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.18337</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.04999</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14031</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.2992</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.309</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36593</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33587</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.31995</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.3102</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40508</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32022</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.302</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31423</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.3004</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.16984</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.15646</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.1686</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.14582</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15718</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15646</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.2327</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.2119</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22474</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.268</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.285</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.2797</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.2697</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.3224</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.392</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.43779</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.48234</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.42665</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40799</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.2992</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15669</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.3145</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.321</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.326</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.50763</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62201</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49794</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78099</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92031</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.4945</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.92111</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8842300000000001</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.30778</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.37476</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.9084500000000001</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63524</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.2077</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.55935</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.35195</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.04742</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.55191</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.80889</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5303</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7918200000000001</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.87899</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.88327</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.50997</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.41511</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.42117</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.46899</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.22828</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87899</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.5511200000000001</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6430800000000001</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.54344</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.50364</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45824</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42659</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.44074</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45075</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39343</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45275</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42087</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.3544</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36523</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.39062</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41476</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34386</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39065</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.35214</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.35639</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.40781</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.35831</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.4508</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58761</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42768</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.59596</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.6017100000000001</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.66883</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46542</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.59373</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.87387</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.5970700000000001</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.88335</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.83793</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.86798</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.43935</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.3303</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.33154</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.73826</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.43194</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.29594</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32021</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.3303</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33147</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.344</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30429</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29337</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31023</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.313</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.3233</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45236</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.354</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9109299999999999</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.35979</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.46402</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.49079</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.40256</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.45579</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.38274</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.4104</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.3569</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.36005</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.34983</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35864</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.3504</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.365</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33456</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33794</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31146</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.292</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16551</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30842</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.32984</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.33132</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.32053</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.262</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.19031</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.29253</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.34167</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.33319</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.33303</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.31355</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.31155</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.31058</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.3133</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25559</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.29064</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.34824</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.2801</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32897</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32297</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38552</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.33497</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.43517</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.32847</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35124</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44836</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.4204</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35895</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40168</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.4004</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59663</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.59658</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.14104</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.69769</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.78771</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.64777</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.5789800000000001</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43956</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43711</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41476</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.3902</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42768</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39608</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43375</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.44635</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.35495</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.29441</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30842</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.33378</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30178</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.2501</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.70913</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.28977</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.29313</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.29063</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.32701</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.33478</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.29416</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.2392</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.2793</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.2782</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.27569</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.29837</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.319</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.4537</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.464</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.76418</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46542</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43832</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.38213</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.5026</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.3869</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.3248</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42373</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.3446</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.336</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.3244</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.3193</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.339</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.31741</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0.3173</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.3007</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.2425</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.15282</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.15675</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.1639</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0.12841</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0.19432</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.14668</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.14813</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14668</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.14813</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.266</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.14813</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.14813</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.16094</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.11722</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.11685</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.16017</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.14813</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.15248</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.2964</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.32875</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.33411</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.36771</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34648</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39672</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.4498</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.3908</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39799</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.44388</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.43939</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44431</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44431</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.4029700000000001</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.3908</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39799</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.3923</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.348</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.34932</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.5303</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38926</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.46858</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.4237</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41597</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38202</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36969</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.3908</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34704</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.32657</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.33443</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.3137799999999999</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.31752</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.29014</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.29558</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.205</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.33157</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.2561</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.26071</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30755</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.29535</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31525</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.30941</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.38235</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.337</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.3001</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.29554</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.34073</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.33598</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.34614</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.33563</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.3327</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.32648</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.3239</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.33406</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.36126</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36486</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.37112</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.35999</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.37164</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.34244</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38199</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.3556</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.35758</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41476</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.3506</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36705</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.36999</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36624</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.4201</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37043</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.5155299999999999</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.3473</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.34571</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34155</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33525</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.35524</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.35319</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.39875</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.35758</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32681</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.32446</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.38891</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.35988</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.3899</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.40008</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.43887</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.34195</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.43521</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.6648999999999999</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.40431</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.40538</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.82187</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.80165</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.275</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.34424</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.35356</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.7247400000000001</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.29741</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.9113600000000001</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.39136</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.29606</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.30697</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.30426</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.32123</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.6107899999999999</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.34932</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.33123</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.41187</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.33564</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.33558</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.33975</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.34681</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31005</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.42632</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32781</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.32678</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.33365</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.33232</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.424</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.41661</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.6762899999999999</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.35644</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.40191</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.32918</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.34859</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.49771</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.33466</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.37968</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.29791</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.32224</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32652</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.34474</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.32939</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.40017</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.32758</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.35235</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.31976</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.46875</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.37606</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.33488</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.35033</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.35531</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.34754</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.33166</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32937</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.33062</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32581</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32446</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.34122</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.34254</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.3337</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.34612</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.34122</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.3243</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.33933</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.34843</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.33808</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.29021</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31842</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.32391</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33244</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.38967</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.3279</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.3143</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.3063</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.3243</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.34124</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34386</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.367</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37155</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39154</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37155</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35494</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.35028</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.3468</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33695</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33868</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33701</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33622</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33165</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.3365</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32573</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.318</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32435</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.3303</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32222</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.3336</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.35624</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35441</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36669</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.37377</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.37782</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.39996</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37719</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.37018</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.63988</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.75419</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.44562</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.37982</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.44026</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.3753</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35206</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.345</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.35111</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41172</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37633</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37082</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36203</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35913</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.35879</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36195</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35882</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.3589</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35275</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35991</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.36021</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35635</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.35918</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35935</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35968</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.37212</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.3587</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35641</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35169</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35849</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33347</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.3258</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26533</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.14813</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28505</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.284</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19865</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.25538</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.21943</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.26192</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28505</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.27828</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28997</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.29122</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.32113</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.3261</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.30708</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.29952</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.34546</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.32228</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.33915</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.33313</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.33226</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.31298</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.32996</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.3142</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.6441699999999999</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.60754</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.6047100000000001</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.47682</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.70278</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.47935</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.80828</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.50307</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.48664</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.40622</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37767</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.47819</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.4303</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37863</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37476</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36717</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.36002</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3455</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.49261</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.5273600000000001</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.5151399999999999</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.6871499999999999</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.44958</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40593</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41845</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.4006</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.397</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39387</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38763</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41845</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38763</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41686</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41265</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.44959</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.56031</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45022</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.84919</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.45099</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.435</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.354</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.43606</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.43939</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.53886</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.4407</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.29375</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32587</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.35707</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.38875</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.38564</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.4028</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.35769</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.32396</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.31644</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.32152</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.32403</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.38154</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.5894400000000001</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.32609</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.57499</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.32615</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.33234</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.32936</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.30486</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33236</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.35008</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.37112</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.36916</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.3547</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.35086</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.37923</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.40873</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.4276</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.49048</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.43944</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.51301</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.51627</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.55377</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.7046699999999999</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.73073</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.71496</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.69782</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.80904</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.5831799999999999</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.52874</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.846</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.78099</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.62503</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.6765</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.46991</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.48836</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.48125</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.47597</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.4207</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.55475</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.4303</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.44471</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.46077</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.43974</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.42848</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.4016</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.40804</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.38922</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.3568</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.3758</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36578</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38688</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.3666</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35522</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39819</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.3956</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38688</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.3515</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.34153</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.35735</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.18497</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.40052</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.3243</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1.34775</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.37465</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.4059700000000001</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.37911</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.449</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.39056</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.46056</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.3151</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.29943</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.10954</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.17642</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.29275</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29022</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.34967</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34785</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34982</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.36966</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.35966</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.36272</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.35816</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.35437</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.38579</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.39554</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.3758</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.36452</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.37212</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.39228</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.3785</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44431</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.3601</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.40552</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.39592</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.35101</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.381</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.361</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.35661</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.34919</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.36082</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.335</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.33619</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.31762</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.32648</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.32489</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.33642</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.27579</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.32967</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.31367</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.3243</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.22652</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28678</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.22938</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.28687</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.24907</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.25289</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.14668</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.29997</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29775</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.33472</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.2485</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25007</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.16918</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.17046</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.25806</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30285</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30546</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.22813</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.2774</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.25212</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.28501</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28413</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.30674</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.35418</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.38535</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.3528</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.38663</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.39845</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.40286</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.40083</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35317</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.38299</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35232</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36777</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36675</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.37174</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36509</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.38251</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.3656</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.352</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.343</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34587</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.315</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.3104</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.3101</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.30999</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.3084</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.30499</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.3053</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.306</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.3064</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.26827</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.2543</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.17387</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.21629</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.23943</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01749</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.02545</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.11775</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.01145</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.02917</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02852</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.03922999999999999</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.04999</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0.28481</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.00175</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.33005</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04976</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.03153</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.04273</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.19421</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.20713</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.24397</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.2801</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.27103</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.27199</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.27088</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.27693</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.30017</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.30036</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.29761</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.30999</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.30977</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.32774</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.30076</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.29808</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.31421</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.30648</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.34485</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.45053</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.34359</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.35227</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.32614</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.3158</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.30089</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.30459</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.446</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.16988</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.71287</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.61441</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.19937</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.35897</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.32909</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.30936</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.3547</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.31335</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.33969</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.32438</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.2951</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.26533</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.25736</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.2951</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.26758</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.24178</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.2749</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.25802</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.32411</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.28815</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.26607</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.32932</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.30642</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.33111</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.37085</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.32135</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.28996</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.29145</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.24593</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.19611</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.7449</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.6821699999999999</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.68465</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.7088</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.18083</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.34138</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.207</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.26293</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.24173</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.14998</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.15403</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.11591</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.23492</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.13913</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.32055</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.04078</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.07316</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.12499</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.04999</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.18835</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.02275</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.14812</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.14946</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.16712</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.00634</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.13096</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.13418</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.13651</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.21009</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.2504</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.2904</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.31001</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.32345</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32406</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.32997</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.3503</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.3313</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.3703</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.36512</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.355</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.3708</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.35044</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.325</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.3301</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.38044</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.7760499999999999</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.50084</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.45521</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.48674</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.41756</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.41525</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.37724</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.39443</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34354</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.34839</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.35649</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34487</v>
+      </c>
+      <c r="R138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32278</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.31787</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.29749</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.31062</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.32233</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.30579</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.31621</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.32531</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.535</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.54332</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.3944</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.42391</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.33973</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.32424</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.40785</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.44743</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.34414</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.48968</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.38237</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.44242</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.37105</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.35234</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.43343</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.3222</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30925</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.32581</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31117</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.14838</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.271</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32455</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32429</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.33225</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.27771</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32596</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.291</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32053</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.33753</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.34325</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32702</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33199</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.34419</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.3478</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.3456</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.34794</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.35845</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.36912</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.35799</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.3793</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.35955</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.36336</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33813</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34982</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.41683</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.35845</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37898</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.41066</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.53822</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35664</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.40842</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.35431</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.38902</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.36379</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.41712</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.37327</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.49766</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.38839</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.37624</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.35698</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.36194</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.35481</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>1.20831</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.4406600000000001</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.44912</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.39483</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.42813</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.39373</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.3591</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.45174</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.37337</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.36119</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.404</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.36345</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.34654</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.36191</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33992</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.35986</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.34124</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.31928</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34629</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.34598</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.36394</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35958</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.35327</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.39652</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.369</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.35914</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35926</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.3677</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.38274</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.37128</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.38377</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.70411</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.43115</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.64167</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.36694</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.50173</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.36955</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.35197</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.30093</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.3428</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33468</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.37131</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.34523</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.31464</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.32924</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.25714</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.35031</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32499</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32526</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.32548</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32834</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32909</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.33618</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.36437</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.35315</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.39169</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.38621</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.48538</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.49719</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.47864</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.48564</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.40997</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.37733</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.39731</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.40163</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.46278</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.33417</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.22681</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.36784</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.34776</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.35414</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.32614</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.37117</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.41496</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.3609</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.37141</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.36705</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.46029</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40149</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38927</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.3768</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.45372</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.3726</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.369</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.47621</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.3903</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.3806</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.375</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.37385</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37849</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.3766</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.36872</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.36659</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.36112</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35922</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.3603</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.32725</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35607</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.3471</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37113</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.37585</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.35813</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.36268</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.35963</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.4020899999999999</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.41054</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.37822</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35944</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.45271</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.39448</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.36444</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.24071</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.34444</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31384</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.359</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.30658</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.32024</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33854</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33234</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.3481</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.29614</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.33978</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.33943</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.37863</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.37545</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.35532</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.37999</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.50031</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.39804</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.47405</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.41985</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.41918</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.49494</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.5757100000000001</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.57478</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.34036</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.34867</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.47644</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.49253</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.53972</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.43797</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.46821</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.29526</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.74251</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.9690700000000001</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.59336</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.60293</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39893</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.4458</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39787</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37633</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.37922</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.3756</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.24096</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.3696</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.3386</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.36836</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.34037</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.34756</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.33363</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33765</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34438</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.34238</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.33945</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.36486</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.34189</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.34198</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.34376</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.32436</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.33035</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32498</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.32694</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.3256</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.32818</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.32578</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.32285</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.35446</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.37204</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.3362</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.32489</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.31958</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.31471</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.3103399999999999</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.34378</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.2991</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.31863</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32326</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.2062</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.24964</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.14871</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.2638</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.14134</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.05300999999999999</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.35859</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.33604</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.16859</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.31294</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.1877</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.16112</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.007</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.14899</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.04348</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.05023</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.21772</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.0648</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.0486</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.16788</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.13935</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.15845</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.33417</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.30599</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.31744</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.33337</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.35539</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.33799</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.34172</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.36107</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.21803</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.33674</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.3122799999999999</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.36881</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.34456</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.40366</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.37462</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.40163</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.41132</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.37579</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.39122</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.41847</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.38023</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.38852</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.40709</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.36513</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.43006</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.37624</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.36924</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.35627</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.36886</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.3642</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.89327</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.36833</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.47631</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.4285</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.41857</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.34607</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.3908</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.42399</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.38587</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.3643</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.37605</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.35666</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.37182</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.36124</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.35647</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38312</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.40906</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.37783</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.37506</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.36427</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36663</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.37388</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.3633</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35136</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.41357</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.35048</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.35717</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.34306</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.31341</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.33902</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.32297</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.34343</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.32768</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.31773</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.2984</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.22194</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.22365</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.25586</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.22988</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.35798</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.33569</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.34207</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.33383</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.70166</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.36908</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.01749</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.68757</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.14788</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.34657</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.74551</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.51902</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.61483</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.6523099999999999</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.26035</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.49942</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.33846</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35725</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.31694</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.3008</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.33742</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.32571</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.36978</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.33414</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.49773</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.39976</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.39629</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.34981</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.36916</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.32729</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.39295</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.6085</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.37976</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.35647</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.35712</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.36129</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.34267</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.36927</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.33138</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.40821</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.38646</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.36955</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.3772799999999999</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.3647</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35509</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.36721</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.36196</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.33852</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.68165</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.37516</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.37689</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.35822</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37623</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.37368</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.35783</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.5387799999999999</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.36881</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.4136</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.38657</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.35713</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.35557</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35847</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.3505</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.34531</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33553</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.34331</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33609</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.34775</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.34196</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34321</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34483</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.35611</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.34599</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.32056</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.29031</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.27728</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.15091</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.29578</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.24427</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.24858</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.12333</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.18613</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>-0.03578</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04325</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.43944</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.34033</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.54161</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>1.10223</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.43256</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.43781</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.32056</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.50384</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.18173</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.20975</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.12731</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.27658</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.2555</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.13603</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.62179</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.2709</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.18491</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.12288</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.26974</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.19813</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.29727</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.26042</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.29698</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.25662</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.28959</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.33235</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.32096</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.31654</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.32183</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.34032</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.33366</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.35272</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.32475</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.32986</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.34993</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.37175</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.34477</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.35025</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.36124</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.34706</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.38293</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.38724</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.45657</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.37024</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.3796</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.37233</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.37868</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.35585</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.36788</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.37205</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.35957</v>
       </c>
     </row>
   </sheetData>
